--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2178,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121143243</v>
+        <v>137005160</v>
       </c>
       <c r="B15" t="n">
-        <v>57141</v>
+        <v>56885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,45 +2189,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100111</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>470898</v>
+        <v>470728</v>
       </c>
       <c r="R15" t="n">
-        <v>6537474</v>
+        <v>6537624</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2251,12 +2253,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>02:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>02:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,27 +2283,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143243</t>
+          <t>https://artportalen.se/Sighting/137005160</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113140127</v>
+        <v>121143243</v>
       </c>
       <c r="B16" t="n">
-        <v>4775</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,43 +2311,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>470876</v>
+        <v>470898</v>
       </c>
       <c r="R16" t="n">
-        <v>6537522</v>
+        <v>6537474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,12 +2373,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,7 +2387,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2394,13 +2404,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140127</t>
+          <t>https://artportalen.se/Sighting/121143243</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121143237</v>
+        <v>113140127</v>
       </c>
       <c r="B17" t="n">
         <v>4775</v>
@@ -2434,20 +2444,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>470868</v>
+        <v>470876</v>
       </c>
       <c r="R17" t="n">
-        <v>6537537</v>
+        <v>6537522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2474,17 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,16 +2516,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143237</t>
+          <t>https://artportalen.se/Sighting/113140127</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113140114</v>
+        <v>121143237</v>
       </c>
       <c r="B18" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,21 +2533,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,20 +2556,20 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>470865</v>
+        <v>470868</v>
       </c>
       <c r="R18" t="n">
-        <v>6537532</v>
+        <v>6537537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2591,12 +2596,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,13 +2633,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140114</t>
+          <t>https://artportalen.se/Sighting/121143237</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113140122</v>
+        <v>113140114</v>
       </c>
       <c r="B19" t="n">
         <v>5179</v>
@@ -2673,10 +2683,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>470876</v>
+        <v>470865</v>
       </c>
       <c r="R19" t="n">
-        <v>6537522</v>
+        <v>6537532</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2735,13 +2745,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140122</t>
+          <t>https://artportalen.se/Sighting/113140114</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113140175</v>
+        <v>113140122</v>
       </c>
       <c r="B20" t="n">
         <v>5179</v>
@@ -2785,10 +2795,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>470900</v>
+        <v>470876</v>
       </c>
       <c r="R20" t="n">
-        <v>6537473</v>
+        <v>6537522</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2847,13 +2857,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140175</t>
+          <t>https://artportalen.se/Sighting/113140122</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113140184</v>
+        <v>113140175</v>
       </c>
       <c r="B21" t="n">
         <v>5179</v>
@@ -2897,7 +2907,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>470907</v>
+        <v>470900</v>
       </c>
       <c r="R21" t="n">
         <v>6537473</v>
@@ -2959,13 +2969,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140184</t>
+          <t>https://artportalen.se/Sighting/113140175</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113140220</v>
+        <v>113140184</v>
       </c>
       <c r="B22" t="n">
         <v>5179</v>
@@ -3009,10 +3019,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>470913</v>
+        <v>470907</v>
       </c>
       <c r="R22" t="n">
-        <v>6537469</v>
+        <v>6537473</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,13 +3081,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140220</t>
+          <t>https://artportalen.se/Sighting/113140184</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113140273</v>
+        <v>113140220</v>
       </c>
       <c r="B23" t="n">
         <v>5179</v>
@@ -3121,10 +3131,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471045</v>
+        <v>470913</v>
       </c>
       <c r="R23" t="n">
-        <v>6537610</v>
+        <v>6537469</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,13 +3193,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140273</t>
+          <t>https://artportalen.se/Sighting/113140220</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121143236</v>
+        <v>113140273</v>
       </c>
       <c r="B24" t="n">
         <v>5179</v>
@@ -3223,20 +3233,20 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>470861</v>
+        <v>471045</v>
       </c>
       <c r="R24" t="n">
-        <v>6537538</v>
+        <v>6537610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3263,17 +3273,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,16 +3305,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143236</t>
+          <t>https://artportalen.se/Sighting/113140273</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129206663</v>
+        <v>121143236</v>
       </c>
       <c r="B25" t="n">
-        <v>57947</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,42 +3322,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102977</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>470833</v>
+        <v>470861</v>
       </c>
       <c r="R25" t="n">
-        <v>6537406</v>
+        <v>6537538</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3376,27 +3385,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Kly, kly, kly.</t>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3405,61 +3404,62 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129206663</t>
+          <t>https://artportalen.se/Sighting/121143236</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129379827</v>
+        <v>129206663</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>57947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3468,10 +3468,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>470865</v>
+        <v>470833</v>
       </c>
       <c r="R26" t="n">
-        <v>6537633</v>
+        <v>6537406</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3498,27 +3498,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Förekomst spridd över perioden</t>
+          <t>Kly, kly, kly.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3533,74 +3533,70 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129379827</t>
+          <t>https://artportalen.se/Sighting/129206663</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113140126</v>
+        <v>129379827</v>
       </c>
       <c r="B27" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Vg</t>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>470876</v>
+        <v>470865</v>
       </c>
       <c r="R27" t="n">
-        <v>6537522</v>
+        <v>6537633</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3624,12 +3620,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>07:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Förekomst spridd över perioden</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3638,31 +3649,30 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140126</t>
+          <t>https://artportalen.se/Sighting/129379827</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113140282</v>
+        <v>113140126</v>
       </c>
       <c r="B28" t="n">
         <v>5199</v>
@@ -3706,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>471040</v>
+        <v>470876</v>
       </c>
       <c r="R28" t="n">
-        <v>6537607</v>
+        <v>6537522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3768,16 +3778,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140282</t>
+          <t>https://artportalen.se/Sighting/113140126</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113140109</v>
+        <v>113140282</v>
       </c>
       <c r="B29" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3785,21 +3795,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3818,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>470867</v>
+        <v>471040</v>
       </c>
       <c r="R29" t="n">
-        <v>6537516</v>
+        <v>6537607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3880,13 +3890,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140109</t>
+          <t>https://artportalen.se/Sighting/113140282</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>113140275</v>
+        <v>113140109</v>
       </c>
       <c r="B30" t="n">
         <v>8444</v>
@@ -3930,10 +3940,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>471045</v>
+        <v>470867</v>
       </c>
       <c r="R30" t="n">
-        <v>6537610</v>
+        <v>6537516</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3992,16 +4002,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113140275</t>
+          <t>https://artportalen.se/Sighting/113140109</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121143244</v>
+        <v>113140275</v>
       </c>
       <c r="B31" t="n">
-        <v>99153</v>
+        <v>8444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4009,42 +4019,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219874</v>
+        <v>106554</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>470861</v>
+        <v>471045</v>
       </c>
       <c r="R31" t="n">
-        <v>6537510</v>
+        <v>6537610</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4071,12 +4082,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,6 +4096,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4102,62 +4114,60 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143244</t>
+          <t>https://artportalen.se/Sighting/113140275</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121143245</v>
+        <v>137005123</v>
       </c>
       <c r="B32" t="n">
-        <v>99153</v>
+        <v>56866</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>205998</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Vg</t>
+          <t>Norra Välevattnet, Norra Välevattnet, Vg</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>470904</v>
+        <v>470728</v>
       </c>
       <c r="R32" t="n">
-        <v>6537459</v>
+        <v>6537624</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4181,12 +4191,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21:37</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4201,24 +4221,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143245</t>
+          <t>https://artportalen.se/Sighting/137005123</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121143246</v>
+        <v>121143244</v>
       </c>
       <c r="B33" t="n">
         <v>99153</v>
@@ -4261,10 +4281,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>470909</v>
+        <v>470861</v>
       </c>
       <c r="R33" t="n">
-        <v>6537452</v>
+        <v>6537510</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4322,13 +4342,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143246</t>
+          <t>https://artportalen.se/Sighting/121143244</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121143247</v>
+        <v>121143245</v>
       </c>
       <c r="B34" t="n">
         <v>99153</v>
@@ -4371,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>470916</v>
+        <v>470904</v>
       </c>
       <c r="R34" t="n">
-        <v>6537438</v>
+        <v>6537459</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4432,16 +4452,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143247</t>
+          <t>https://artportalen.se/Sighting/121143245</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113140265</v>
+        <v>121143246</v>
       </c>
       <c r="B35" t="n">
-        <v>97983</v>
+        <v>99153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4449,21 +4469,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4477,14 +4497,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Norra Välevattnet, Vg</t>
+          <t>Hallsberg-Laxå, Vg</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>471036</v>
+        <v>470909</v>
       </c>
       <c r="R35" t="n">
-        <v>6537541</v>
+        <v>6537452</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4511,12 +4531,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4525,7 +4545,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4542,6 +4561,227 @@
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143246</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121143247</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hallsberg-Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>470916</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6537438</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-10-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143247</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>113140265</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norra Välevattnet, Vg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>471036</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6537541</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113140265</t>
         </is>
@@ -4583,6 +4823,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>137005160</v>
       </c>
       <c r="B15" t="n">
-        <v>56885</v>
+        <v>56898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137005123</v>
       </c>
       <c r="B32" t="n">
-        <v>56866</v>
+        <v>56879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>137005160</v>
       </c>
       <c r="B15" t="n">
-        <v>56898</v>
+        <v>56900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>137005123</v>
       </c>
       <c r="B32" t="n">
-        <v>56879</v>
+        <v>56881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2207,11 +2207,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>autobox</t>
@@ -4145,11 +4141,7 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>autobox</t>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>137005160</v>
       </c>
       <c r="B15" t="n">
-        <v>56900</v>
+        <v>56910</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>137005123</v>
       </c>
       <c r="B32" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>137005160</v>
       </c>
       <c r="B15" t="n">
-        <v>56910</v>
+        <v>56911</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>137005123</v>
       </c>
       <c r="B32" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 50773-2022 artfynd.xlsx
+++ b/artfynd/A 50773-2022 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>137005160</v>
       </c>
       <c r="B15" t="n">
-        <v>56911</v>
+        <v>56914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>137005123</v>
       </c>
       <c r="B32" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
